--- a/Скрипты/data/КЖ_АБК.xlsx
+++ b/Скрипты/data/КЖ_АБК.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\работа альтэн\ЦВСИГ\ЦСВИГ ИСПОЛН\ЦСВИГ ИСПОЛН (1)\АБК\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B612A32-E7C5-427C-998C-B7C9C1CC0D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845682E0-245F-42EB-8A0C-26EB9103FC44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3549" yWindow="4071" windowWidth="24685" windowHeight="13055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="4" r:id="rId1"/>
     <sheet name="Лист 2" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$F$1:$F$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$F$1:$F$175</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="266">
   <si>
     <t xml:space="preserve">КИС-П </t>
   </si>
@@ -351,9 +351,6 @@
     <t>UR3</t>
   </si>
   <si>
-    <t>СПС</t>
-  </si>
-  <si>
     <t>2SC1.24..25</t>
   </si>
   <si>
@@ -820,6 +817,24 @@
   </si>
   <si>
     <t>rs2</t>
+  </si>
+  <si>
+    <t>2BTH1.18,(40)</t>
+  </si>
+  <si>
+    <t>2BTH1.25(60)</t>
+  </si>
+  <si>
+    <t>2BTH1.26(60)</t>
+  </si>
+  <si>
+    <t>2BTH1.27(60)</t>
+  </si>
+  <si>
+    <t>2BTH1.19,(40)</t>
+  </si>
+  <si>
+    <t>АПС,СОУЭ</t>
   </si>
 </sst>
 </file>
@@ -877,7 +892,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -893,6 +908,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -953,7 +974,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -987,16 +1008,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1301,7 +1319,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED1BFC1E-6170-421F-B27F-ADCB2033496C}">
-  <dimension ref="A1:S171"/>
+  <dimension ref="A1:S175"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.15234375" style="14"/>
@@ -1340,7 +1358,7 @@
         <v>4</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>101</v>
@@ -1370,7 +1388,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>101</v>
@@ -1400,7 +1418,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>101</v>
@@ -1430,7 +1448,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>101</v>
@@ -1460,7 +1478,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>101</v>
@@ -1490,7 +1508,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>101</v>
@@ -1520,7 +1538,7 @@
         <v>4</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>101</v>
@@ -1553,7 +1571,7 @@
         <v>4</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>101</v>
@@ -1583,7 +1601,7 @@
         <v>4</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>101</v>
@@ -1613,7 +1631,7 @@
         <v>4</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>101</v>
@@ -1643,7 +1661,7 @@
         <v>4</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>101</v>
@@ -1673,7 +1691,7 @@
         <v>4</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F13" s="12" t="s">
         <v>101</v>
@@ -1703,7 +1721,7 @@
         <v>4</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F14" s="12" t="s">
         <v>101</v>
@@ -1733,7 +1751,7 @@
         <v>4</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F15" s="12" t="s">
         <v>101</v>
@@ -1763,7 +1781,7 @@
         <v>4</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F16" s="12" t="s">
         <v>101</v>
@@ -1793,7 +1811,7 @@
         <v>4</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F17" s="12" t="s">
         <v>101</v>
@@ -1823,7 +1841,7 @@
         <v>4</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F18" s="12" t="s">
         <v>101</v>
@@ -1853,7 +1871,7 @@
         <v>4</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F19" s="12" t="s">
         <v>101</v>
@@ -1883,7 +1901,7 @@
         <v>4</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F20" s="12" t="s">
         <v>101</v>
@@ -1913,7 +1931,7 @@
         <v>4</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F21" s="12" t="s">
         <v>101</v>
@@ -1943,7 +1961,7 @@
         <v>4</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F22" s="12" t="s">
         <v>101</v>
@@ -1973,7 +1991,7 @@
         <v>4</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F23" s="12" t="s">
         <v>101</v>
@@ -2003,7 +2021,7 @@
         <v>4</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F24" s="12" t="s">
         <v>101</v>
@@ -2033,17 +2051,17 @@
         <v>58</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G25" s="8">
         <v>27</v>
       </c>
       <c r="H25" s="10"/>
       <c r="I25" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J25" s="8">
         <v>27</v>
@@ -2063,17 +2081,17 @@
         <v>58</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G26" s="8">
         <v>19</v>
       </c>
       <c r="H26" s="10"/>
       <c r="I26" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J26" s="8">
         <v>19</v>
@@ -2093,17 +2111,17 @@
         <v>58</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G27" s="8">
         <v>19</v>
       </c>
       <c r="H27" s="10"/>
       <c r="I27" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J27" s="8">
         <v>19</v>
@@ -2123,17 +2141,17 @@
         <v>58</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G28" s="8">
         <v>30</v>
       </c>
       <c r="H28" s="10"/>
       <c r="I28" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J28" s="8">
         <v>30</v>
@@ -2141,7 +2159,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29" s="16" t="s">
-        <v>104</v>
+        <v>265</v>
       </c>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
@@ -2170,7 +2188,7 @@
         <v>69</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G30" s="12">
         <v>3.1</v>
@@ -2179,7 +2197,7 @@
         <v>70</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J30" s="12">
         <v>4</v>
@@ -2202,7 +2220,7 @@
         <v>69</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G31" s="12">
         <v>1.9</v>
@@ -2211,7 +2229,7 @@
         <v>70</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J31" s="12">
         <v>2</v>
@@ -2234,7 +2252,7 @@
         <v>69</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G32" s="12">
         <v>10.8</v>
@@ -2243,7 +2261,7 @@
         <v>70</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J32" s="12">
         <v>11</v>
@@ -2257,7 +2275,7 @@
         <v>72</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D33" s="12" t="s">
         <v>68</v>
@@ -2266,7 +2284,7 @@
         <v>69</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G33" s="12">
         <v>1.9</v>
@@ -2275,7 +2293,7 @@
         <v>70</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J33" s="12">
         <v>2</v>
@@ -2286,11 +2304,11 @@
         <v>65</v>
       </c>
       <c r="B34" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="12" t="s">
-        <v>107</v>
-      </c>
       <c r="D34" s="12" t="s">
         <v>68</v>
       </c>
@@ -2298,7 +2316,7 @@
         <v>69</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G34" s="12">
         <v>3.9</v>
@@ -2307,7 +2325,7 @@
         <v>70</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J34" s="12">
         <v>3</v>
@@ -2318,11 +2336,11 @@
         <v>65</v>
       </c>
       <c r="B35" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C35" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="C35" s="12" t="s">
-        <v>108</v>
-      </c>
       <c r="D35" s="12" t="s">
         <v>68</v>
       </c>
@@ -2330,7 +2348,7 @@
         <v>69</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G35" s="12">
         <v>4.5999999999999996</v>
@@ -2339,7 +2357,7 @@
         <v>70</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J35" s="12">
         <v>5</v>
@@ -2350,11 +2368,11 @@
         <v>65</v>
       </c>
       <c r="B36" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C36" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="C36" s="12" t="s">
-        <v>109</v>
-      </c>
       <c r="D36" s="12" t="s">
         <v>68</v>
       </c>
@@ -2362,7 +2380,7 @@
         <v>69</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G36" s="12">
         <v>7.4</v>
@@ -2371,7 +2389,7 @@
         <v>70</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J36" s="12">
         <v>8</v>
@@ -2382,11 +2400,11 @@
         <v>65</v>
       </c>
       <c r="B37" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C37" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="C37" s="12" t="s">
-        <v>110</v>
-      </c>
       <c r="D37" s="12" t="s">
         <v>68</v>
       </c>
@@ -2394,7 +2412,7 @@
         <v>69</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G37" s="12">
         <v>10.1</v>
@@ -2403,7 +2421,7 @@
         <v>70</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J37" s="12">
         <v>11</v>
@@ -2414,11 +2432,11 @@
         <v>65</v>
       </c>
       <c r="B38" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C38" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="C38" s="12" t="s">
-        <v>111</v>
-      </c>
       <c r="D38" s="12" t="s">
         <v>68</v>
       </c>
@@ -2426,7 +2444,7 @@
         <v>69</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G38" s="12">
         <v>6.1</v>
@@ -2435,7 +2453,7 @@
         <v>70</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J38" s="12">
         <v>7</v>
@@ -2446,11 +2464,11 @@
         <v>65</v>
       </c>
       <c r="B39" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="C39" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="C39" s="12" t="s">
-        <v>112</v>
-      </c>
       <c r="D39" s="12" t="s">
         <v>68</v>
       </c>
@@ -2458,7 +2476,7 @@
         <v>69</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G39" s="12">
         <v>6.5</v>
@@ -2467,7 +2485,7 @@
         <v>70</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J39" s="12">
         <v>7</v>
@@ -2478,11 +2496,11 @@
         <v>65</v>
       </c>
       <c r="B40" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="C40" s="12" t="s">
-        <v>113</v>
-      </c>
       <c r="D40" s="12" t="s">
         <v>68</v>
       </c>
@@ -2490,7 +2508,7 @@
         <v>69</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G40" s="12">
         <v>9.6999999999999993</v>
@@ -2499,7 +2517,7 @@
         <v>70</v>
       </c>
       <c r="I40" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J40" s="12">
         <v>10</v>
@@ -2510,11 +2528,11 @@
         <v>65</v>
       </c>
       <c r="B41" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C41" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="C41" s="12" t="s">
-        <v>114</v>
-      </c>
       <c r="D41" s="12" t="s">
         <v>68</v>
       </c>
@@ -2522,7 +2540,7 @@
         <v>69</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G41" s="12">
         <v>10.4</v>
@@ -2531,7 +2549,7 @@
         <v>70</v>
       </c>
       <c r="I41" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J41" s="12">
         <v>11</v>
@@ -2542,7 +2560,7 @@
         <v>65</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C42" s="12" t="s">
         <v>73</v>
@@ -2554,7 +2572,7 @@
         <v>69</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G42" s="12">
         <v>7.3</v>
@@ -2563,7 +2581,7 @@
         <v>70</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J42" s="12">
         <v>8</v>
@@ -2586,7 +2604,7 @@
         <v>69</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G43" s="12">
         <v>3.7</v>
@@ -2595,7 +2613,7 @@
         <v>70</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J43" s="12">
         <v>5</v>
@@ -2618,7 +2636,7 @@
         <v>69</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G44" s="12">
         <v>2.1</v>
@@ -2627,7 +2645,7 @@
         <v>70</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J44" s="12">
         <v>3</v>
@@ -2641,7 +2659,7 @@
         <v>75</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D45" s="12" t="s">
         <v>68</v>
@@ -2650,7 +2668,7 @@
         <v>69</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G45" s="12">
         <v>3.7</v>
@@ -2659,7 +2677,7 @@
         <v>70</v>
       </c>
       <c r="I45" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J45" s="12">
         <v>4</v>
@@ -2670,11 +2688,11 @@
         <v>65</v>
       </c>
       <c r="B46" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C46" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="C46" s="12" t="s">
-        <v>116</v>
-      </c>
       <c r="D46" s="12" t="s">
         <v>68</v>
       </c>
@@ -2682,7 +2700,7 @@
         <v>69</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G46" s="12">
         <v>6.6</v>
@@ -2691,7 +2709,7 @@
         <v>70</v>
       </c>
       <c r="I46" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J46" s="12">
         <v>7</v>
@@ -2702,11 +2720,11 @@
         <v>65</v>
       </c>
       <c r="B47" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C47" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C47" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="D47" s="12" t="s">
         <v>68</v>
       </c>
@@ -2714,7 +2732,7 @@
         <v>69</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G47" s="12">
         <v>4.2</v>
@@ -2723,7 +2741,7 @@
         <v>70</v>
       </c>
       <c r="I47" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J47" s="12">
         <v>5</v>
@@ -2734,11 +2752,11 @@
         <v>65</v>
       </c>
       <c r="B48" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C48" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="C48" s="12" t="s">
-        <v>118</v>
-      </c>
       <c r="D48" s="12" t="s">
         <v>68</v>
       </c>
@@ -2746,7 +2764,7 @@
         <v>69</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G48" s="12">
         <v>8.6</v>
@@ -2755,7 +2773,7 @@
         <v>70</v>
       </c>
       <c r="I48" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J48" s="12">
         <v>10</v>
@@ -2766,11 +2784,11 @@
         <v>65</v>
       </c>
       <c r="B49" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C49" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="C49" s="12" t="s">
-        <v>119</v>
-      </c>
       <c r="D49" s="12" t="s">
         <v>68</v>
       </c>
@@ -2778,7 +2796,7 @@
         <v>69</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G49" s="12">
         <v>8.4</v>
@@ -2787,7 +2805,7 @@
         <v>70</v>
       </c>
       <c r="I49" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J49" s="12">
         <v>10</v>
@@ -2798,11 +2816,11 @@
         <v>65</v>
       </c>
       <c r="B50" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C50" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="C50" s="12" t="s">
-        <v>120</v>
-      </c>
       <c r="D50" s="12" t="s">
         <v>68</v>
       </c>
@@ -2810,7 +2828,7 @@
         <v>69</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G50" s="12">
         <v>7.2</v>
@@ -2819,7 +2837,7 @@
         <v>70</v>
       </c>
       <c r="I50" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J50" s="12">
         <v>8</v>
@@ -2830,11 +2848,11 @@
         <v>65</v>
       </c>
       <c r="B51" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C51" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="C51" s="12" t="s">
-        <v>121</v>
-      </c>
       <c r="D51" s="12" t="s">
         <v>68</v>
       </c>
@@ -2842,7 +2860,7 @@
         <v>69</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G51" s="12">
         <v>8.8000000000000007</v>
@@ -2851,7 +2869,7 @@
         <v>70</v>
       </c>
       <c r="I51" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J51" s="12">
         <v>9</v>
@@ -2862,10 +2880,10 @@
         <v>65</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D52" s="12" t="s">
         <v>68</v>
@@ -2874,7 +2892,7 @@
         <v>69</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G52" s="12">
         <v>7</v>
@@ -2883,7 +2901,7 @@
         <v>70</v>
       </c>
       <c r="I52" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J52" s="12">
         <v>10</v>
@@ -2897,7 +2915,7 @@
         <v>76</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D53" s="12" t="s">
         <v>68</v>
@@ -2906,7 +2924,7 @@
         <v>69</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G53" s="12">
         <v>2.7</v>
@@ -2915,7 +2933,7 @@
         <v>70</v>
       </c>
       <c r="I53" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J53" s="12">
         <v>3</v>
@@ -2926,7 +2944,7 @@
         <v>65</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C54" s="12" t="s">
         <v>77</v>
@@ -2938,7 +2956,7 @@
         <v>69</v>
       </c>
       <c r="F54" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G54" s="12">
         <v>0.5</v>
@@ -2947,7 +2965,7 @@
         <v>70</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J54" s="12">
         <v>1</v>
@@ -2970,7 +2988,7 @@
         <v>69</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G55" s="12">
         <v>1.4</v>
@@ -2979,7 +2997,7 @@
         <v>70</v>
       </c>
       <c r="I55" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J55" s="12">
         <v>2</v>
@@ -3002,7 +3020,7 @@
         <v>69</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G56" s="12">
         <v>2</v>
@@ -3011,138 +3029,122 @@
         <v>70</v>
       </c>
       <c r="I56" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J56" s="12">
         <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="12" t="s">
-        <v>81</v>
-      </c>
+      <c r="A57" s="12"/>
       <c r="B57" s="12" t="s">
-        <v>102</v>
+        <v>260</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>82</v>
+        <v>261</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E57" s="12" t="s">
         <v>69</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="G57" s="12">
         <v>5</v>
       </c>
-      <c r="H57" s="12" t="s">
-        <v>70</v>
-      </c>
+      <c r="H57" s="12"/>
       <c r="I57" s="12" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="J57" s="12">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="12" t="s">
-        <v>81</v>
-      </c>
+      <c r="A58" s="12"/>
       <c r="B58" s="12" t="s">
-        <v>82</v>
+        <v>261</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>83</v>
+        <v>262</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E58" s="12" t="s">
         <v>69</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="G58" s="12">
-        <v>4</v>
-      </c>
-      <c r="H58" s="12" t="s">
-        <v>70</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="H58" s="12"/>
       <c r="I58" s="12" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="J58" s="12">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="12" t="s">
-        <v>81</v>
-      </c>
+      <c r="A59" s="12"/>
       <c r="B59" s="12" t="s">
-        <v>83</v>
+        <v>261</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>84</v>
+        <v>263</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E59" s="12" t="s">
         <v>69</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="G59" s="12">
         <v>9</v>
       </c>
-      <c r="H59" s="12" t="s">
-        <v>70</v>
-      </c>
+      <c r="H59" s="12"/>
       <c r="I59" s="12" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="J59" s="12">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="12" t="s">
-        <v>81</v>
-      </c>
+      <c r="A60" s="12"/>
       <c r="B60" s="12" t="s">
-        <v>84</v>
+        <v>263</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>85</v>
+        <v>264</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E60" s="12" t="s">
         <v>69</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="G60" s="12">
-        <v>7</v>
-      </c>
-      <c r="H60" s="12" t="s">
-        <v>70</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H60" s="12"/>
       <c r="I60" s="12" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="J60" s="12">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
@@ -3150,10 +3152,10 @@
         <v>81</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D61" s="12" t="s">
         <v>79</v>
@@ -3165,7 +3167,7 @@
         <v>80</v>
       </c>
       <c r="G61" s="12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H61" s="12" t="s">
         <v>70</v>
@@ -3174,7 +3176,7 @@
         <v>80</v>
       </c>
       <c r="J61" s="12">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
@@ -3182,10 +3184,10 @@
         <v>81</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D62" s="12" t="s">
         <v>79</v>
@@ -3197,7 +3199,7 @@
         <v>80</v>
       </c>
       <c r="G62" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H62" s="12" t="s">
         <v>70</v>
@@ -3206,7 +3208,7 @@
         <v>80</v>
       </c>
       <c r="J62" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
@@ -3214,10 +3216,10 @@
         <v>81</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D63" s="12" t="s">
         <v>79</v>
@@ -3229,7 +3231,7 @@
         <v>80</v>
       </c>
       <c r="G63" s="12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H63" s="12" t="s">
         <v>70</v>
@@ -3238,7 +3240,7 @@
         <v>80</v>
       </c>
       <c r="J63" s="12">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
@@ -3246,10 +3248,10 @@
         <v>81</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D64" s="12" t="s">
         <v>79</v>
@@ -3261,7 +3263,7 @@
         <v>80</v>
       </c>
       <c r="G64" s="12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H64" s="12" t="s">
         <v>70</v>
@@ -3270,7 +3272,7 @@
         <v>80</v>
       </c>
       <c r="J64" s="12">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
@@ -3278,10 +3280,10 @@
         <v>81</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D65" s="12" t="s">
         <v>79</v>
@@ -3293,7 +3295,7 @@
         <v>80</v>
       </c>
       <c r="G65" s="12">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H65" s="12" t="s">
         <v>70</v>
@@ -3302,7 +3304,7 @@
         <v>80</v>
       </c>
       <c r="J65" s="12">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
@@ -3310,10 +3312,10 @@
         <v>81</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D66" s="12" t="s">
         <v>79</v>
@@ -3325,7 +3327,7 @@
         <v>80</v>
       </c>
       <c r="G66" s="12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H66" s="12" t="s">
         <v>70</v>
@@ -3334,7 +3336,7 @@
         <v>80</v>
       </c>
       <c r="J66" s="12">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
@@ -3342,10 +3344,10 @@
         <v>81</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D67" s="12" t="s">
         <v>79</v>
@@ -3357,7 +3359,7 @@
         <v>80</v>
       </c>
       <c r="G67" s="12">
-        <v>6.7</v>
+        <v>8</v>
       </c>
       <c r="H67" s="12" t="s">
         <v>70</v>
@@ -3374,10 +3376,10 @@
         <v>81</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D68" s="12" t="s">
         <v>79</v>
@@ -3389,7 +3391,7 @@
         <v>80</v>
       </c>
       <c r="G68" s="12">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="H68" s="12" t="s">
         <v>70</v>
@@ -3406,10 +3408,10 @@
         <v>81</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D69" s="12" t="s">
         <v>79</v>
@@ -3421,7 +3423,7 @@
         <v>80</v>
       </c>
       <c r="G69" s="12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H69" s="12" t="s">
         <v>70</v>
@@ -3430,7 +3432,7 @@
         <v>80</v>
       </c>
       <c r="J69" s="12">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
@@ -3438,10 +3440,10 @@
         <v>81</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D70" s="12" t="s">
         <v>79</v>
@@ -3453,7 +3455,7 @@
         <v>80</v>
       </c>
       <c r="G70" s="12">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="H70" s="12" t="s">
         <v>70</v>
@@ -3470,10 +3472,10 @@
         <v>81</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D71" s="12" t="s">
         <v>79</v>
@@ -3485,7 +3487,7 @@
         <v>80</v>
       </c>
       <c r="G71" s="12">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="H71" s="12" t="s">
         <v>70</v>
@@ -3494,7 +3496,7 @@
         <v>80</v>
       </c>
       <c r="J71" s="12">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
@@ -3502,10 +3504,10 @@
         <v>81</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D72" s="12" t="s">
         <v>79</v>
@@ -3517,7 +3519,7 @@
         <v>80</v>
       </c>
       <c r="G72" s="12">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="H72" s="12" t="s">
         <v>70</v>
@@ -3526,7 +3528,7 @@
         <v>80</v>
       </c>
       <c r="J72" s="12">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
@@ -3534,10 +3536,10 @@
         <v>81</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D73" s="12" t="s">
         <v>79</v>
@@ -3549,7 +3551,7 @@
         <v>80</v>
       </c>
       <c r="G73" s="12">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="H73" s="12" t="s">
         <v>70</v>
@@ -3566,10 +3568,10 @@
         <v>81</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D74" s="12" t="s">
         <v>79</v>
@@ -3581,7 +3583,7 @@
         <v>80</v>
       </c>
       <c r="G74" s="12">
-        <v>2.9</v>
+        <v>5.8</v>
       </c>
       <c r="H74" s="12" t="s">
         <v>70</v>
@@ -3590,624 +3592,624 @@
         <v>80</v>
       </c>
       <c r="J74" s="12">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A75" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F75" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="G75" s="12">
+        <v>5.7</v>
+      </c>
+      <c r="H75" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I75" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="J75" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A76" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B76" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E76" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F76" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="G76" s="12">
+        <v>6</v>
+      </c>
+      <c r="H76" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I76" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="J76" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A77" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B77" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D77" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E77" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F77" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="G77" s="12">
+        <v>6.7</v>
+      </c>
+      <c r="H77" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I77" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="J77" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A78" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B78" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E78" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F78" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="G78" s="12">
+        <v>2.9</v>
+      </c>
+      <c r="H78" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I78" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="J78" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A79" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="B75" s="12" t="s">
+      <c r="B79" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="C75" s="12" t="s">
+      <c r="C79" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="D75" s="12" t="s">
+      <c r="D79" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="E75" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="F75" s="12" t="s">
+      <c r="E79" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F79" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="G75" s="12">
+      <c r="G79" s="12">
         <v>15</v>
       </c>
-      <c r="H75" s="12"/>
-      <c r="I75" s="12" t="s">
+      <c r="H79" s="12"/>
+      <c r="I79" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="J75" s="12">
+      <c r="J79" s="12">
         <v>15</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A76" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="B76" s="16"/>
-      <c r="C76" s="16"/>
-      <c r="D76" s="16"/>
-      <c r="E76" s="16"/>
-      <c r="F76" s="16"/>
-      <c r="G76" s="16"/>
-      <c r="H76" s="16"/>
-      <c r="I76" s="16"/>
-      <c r="J76" s="16"/>
-    </row>
-    <row r="77" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="E77" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="G77" s="7">
-        <v>10</v>
-      </c>
-      <c r="H77" s="7"/>
-      <c r="I77" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="J77" s="7">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E78" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="G78" s="7">
-        <v>10</v>
-      </c>
-      <c r="H78" s="7"/>
-      <c r="I78" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="J78" s="7">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="E79" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="G79" s="7">
-        <v>10</v>
-      </c>
-      <c r="H79" s="7"/>
-      <c r="I79" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="J79" s="7">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B80" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="D80" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="E80" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="F80" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="G80" s="7">
-        <v>7</v>
-      </c>
-      <c r="H80" s="7"/>
-      <c r="I80" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="J80" s="7">
-        <v>9</v>
-      </c>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A80" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="B80" s="16"/>
+      <c r="C80" s="16"/>
+      <c r="D80" s="16"/>
+      <c r="E80" s="16"/>
+      <c r="F80" s="16"/>
+      <c r="G80" s="16"/>
+      <c r="H80" s="16"/>
+      <c r="I80" s="16"/>
+      <c r="J80" s="16"/>
     </row>
     <row r="81" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A81" s="7" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E81" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F81" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="F81" s="7" t="s">
-        <v>129</v>
-      </c>
       <c r="G81" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H81" s="7"/>
       <c r="I81" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J81" s="7">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="82" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A82" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="D82" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E82" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="E82" s="7" t="s">
-        <v>1</v>
-      </c>
       <c r="F82" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G82" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H82" s="7"/>
       <c r="I82" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J82" s="7">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A83" s="7" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="D83" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E83" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="E83" s="7" t="s">
+      <c r="F83" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="F83" s="7" t="s">
-        <v>129</v>
-      </c>
       <c r="G83" s="7">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H83" s="7"/>
       <c r="I83" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J83" s="7">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="84" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A84" s="7" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E84" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F84" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="F84" s="7" t="s">
-        <v>129</v>
-      </c>
       <c r="G84" s="7">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="H84" s="7"/>
       <c r="I84" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J84" s="7">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A85" s="7" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="D85" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E85" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="E85" s="7" t="s">
+      <c r="F85" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="F85" s="7" t="s">
-        <v>129</v>
-      </c>
       <c r="G85" s="7">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="H85" s="7"/>
       <c r="I85" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J85" s="7">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A86" s="7" t="s">
-        <v>63</v>
+        <v>139</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>256</v>
+        <v>135</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="E86" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F86" s="12" t="s">
-        <v>80</v>
+        <v>126</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>128</v>
       </c>
       <c r="G86" s="7">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H86" s="7"/>
-      <c r="I86" s="12" t="s">
-        <v>80</v>
+      <c r="I86" s="7" t="s">
+        <v>128</v>
       </c>
       <c r="J86" s="7">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A87" s="7" t="s">
-        <v>242</v>
+        <v>141</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="E87" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F87" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G87" s="7">
+        <v>25</v>
+      </c>
+      <c r="H87" s="7"/>
+      <c r="I87" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="J87" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A88" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G88" s="7">
+        <v>25</v>
+      </c>
+      <c r="H88" s="7"/>
+      <c r="I88" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="J88" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A89" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G89" s="7">
+        <v>25</v>
+      </c>
+      <c r="H89" s="7"/>
+      <c r="I89" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="J89" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A90" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="E90" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F90" s="12" t="s">
         <v>80</v>
-      </c>
-      <c r="G87" s="7">
-        <v>1</v>
-      </c>
-      <c r="H87" s="7"/>
-      <c r="I87" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="J87" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A88" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="B88" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="C88" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="E88" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F88" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="G88" s="7">
-        <v>1</v>
-      </c>
-      <c r="H88" s="10"/>
-      <c r="I88" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="J88" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A89" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="B89" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="E89" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F89" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="G89" s="7">
-        <v>1</v>
-      </c>
-      <c r="H89" s="7"/>
-      <c r="I89" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="J89" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A90" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="B90" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="C90" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="E90" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F90" s="12" t="s">
-        <v>153</v>
       </c>
       <c r="G90" s="7">
         <v>1</v>
       </c>
-      <c r="H90" s="10"/>
+      <c r="H90" s="7"/>
       <c r="I90" s="12" t="s">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="J90" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A91" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="B91" s="18"/>
-      <c r="C91" s="18"/>
-      <c r="D91" s="18"/>
-      <c r="E91" s="18"/>
-      <c r="F91" s="18"/>
-      <c r="G91" s="18"/>
-      <c r="H91" s="18"/>
-      <c r="I91" s="18"/>
-      <c r="J91" s="18"/>
-    </row>
-    <row r="92" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A92" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="B92" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="C92" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="D92" s="12" t="s">
-        <v>68</v>
+    <row r="91" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A91" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="E91" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F91" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="G91" s="7">
+        <v>1</v>
+      </c>
+      <c r="H91" s="7"/>
+      <c r="I91" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="J91" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A92" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="B92" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C92" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>256</v>
       </c>
       <c r="E92" s="12" t="s">
         <v>69</v>
       </c>
       <c r="F92" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="G92" s="12">
-        <v>4.8</v>
-      </c>
-      <c r="H92" s="12" t="s">
-        <v>70</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="G92" s="7">
+        <v>1</v>
+      </c>
+      <c r="H92" s="10"/>
       <c r="I92" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="J92" s="12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="B93" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="C93" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="D93" s="12" t="s">
-        <v>68</v>
+        <v>80</v>
+      </c>
+      <c r="J92" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A93" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>257</v>
       </c>
       <c r="E93" s="12" t="s">
         <v>69</v>
       </c>
       <c r="F93" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="G93" s="12">
-        <v>7.7</v>
-      </c>
-      <c r="H93" s="12" t="s">
-        <v>70</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="G93" s="7">
+        <v>1</v>
+      </c>
+      <c r="H93" s="7"/>
       <c r="I93" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="J93" s="12">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="B94" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="C94" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="D94" s="12" t="s">
-        <v>68</v>
+        <v>152</v>
+      </c>
+      <c r="J93" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A94" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="B94" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C94" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>257</v>
       </c>
       <c r="E94" s="12" t="s">
         <v>69</v>
       </c>
       <c r="F94" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="G94" s="12">
-        <v>3.8</v>
-      </c>
-      <c r="H94" s="12" t="s">
-        <v>70</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="G94" s="7">
+        <v>1</v>
+      </c>
+      <c r="H94" s="10"/>
       <c r="I94" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="J94" s="12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="B95" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="C95" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="D95" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E95" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F95" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="G95" s="12">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="H95" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="I95" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="J95" s="12">
-        <v>5</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="J94" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A95" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="B95" s="17"/>
+      <c r="C95" s="17"/>
+      <c r="D95" s="17"/>
+      <c r="E95" s="17"/>
+      <c r="F95" s="17"/>
+      <c r="G95" s="17"/>
+      <c r="H95" s="17"/>
+      <c r="I95" s="17"/>
+      <c r="J95" s="17"/>
     </row>
     <row r="96" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A96" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="B96" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="B96" s="12" t="s">
-        <v>156</v>
-      </c>
       <c r="C96" s="12" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D96" s="12" t="s">
         <v>68</v>
@@ -4216,30 +4218,30 @@
         <v>69</v>
       </c>
       <c r="F96" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G96" s="12">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="H96" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I96" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J96" s="12">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A97" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D97" s="12" t="s">
         <v>68</v>
@@ -4248,30 +4250,30 @@
         <v>69</v>
       </c>
       <c r="F97" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G97" s="12">
-        <v>4.3</v>
+        <v>7.7</v>
       </c>
       <c r="H97" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I97" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J97" s="12">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A98" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D98" s="12" t="s">
         <v>68</v>
@@ -4280,30 +4282,30 @@
         <v>69</v>
       </c>
       <c r="F98" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G98" s="12">
-        <v>6.1</v>
+        <v>3.8</v>
       </c>
       <c r="H98" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I98" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J98" s="12">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A99" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D99" s="12" t="s">
         <v>68</v>
@@ -4312,16 +4314,16 @@
         <v>69</v>
       </c>
       <c r="F99" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G99" s="12">
-        <v>4.2</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="H99" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I99" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J99" s="12">
         <v>5</v>
@@ -4329,13 +4331,13 @@
     </row>
     <row r="100" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A100" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D100" s="12" t="s">
         <v>68</v>
@@ -4344,30 +4346,30 @@
         <v>69</v>
       </c>
       <c r="F100" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G100" s="12">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="H100" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I100" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J100" s="12">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A101" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D101" s="12" t="s">
         <v>68</v>
@@ -4376,30 +4378,30 @@
         <v>69</v>
       </c>
       <c r="F101" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G101" s="12">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="H101" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I101" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J101" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A102" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D102" s="12" t="s">
         <v>68</v>
@@ -4408,30 +4410,30 @@
         <v>69</v>
       </c>
       <c r="F102" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G102" s="12">
-        <v>7.1</v>
+        <v>6.1</v>
       </c>
       <c r="H102" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I102" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J102" s="12">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A103" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D103" s="12" t="s">
         <v>68</v>
@@ -4440,30 +4442,30 @@
         <v>69</v>
       </c>
       <c r="F103" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G103" s="12">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="H103" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I103" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J103" s="12">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A104" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B104" s="12" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D104" s="12" t="s">
         <v>68</v>
@@ -4472,30 +4474,30 @@
         <v>69</v>
       </c>
       <c r="F104" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G104" s="12">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="H104" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I104" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J104" s="12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A105" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B105" s="12" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D105" s="12" t="s">
         <v>68</v>
@@ -4504,30 +4506,30 @@
         <v>69</v>
       </c>
       <c r="F105" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G105" s="12">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="H105" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I105" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J105" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="106" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A106" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B106" s="12" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D106" s="12" t="s">
         <v>68</v>
@@ -4536,30 +4538,30 @@
         <v>69</v>
       </c>
       <c r="F106" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G106" s="12">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="H106" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I106" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J106" s="12">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A107" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B107" s="12" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D107" s="12" t="s">
         <v>68</v>
@@ -4568,30 +4570,30 @@
         <v>69</v>
       </c>
       <c r="F107" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G107" s="12">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="H107" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I107" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J107" s="12">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A108" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B108" s="12" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D108" s="12" t="s">
         <v>68</v>
@@ -4600,30 +4602,30 @@
         <v>69</v>
       </c>
       <c r="F108" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G108" s="12">
-        <v>6.1</v>
+        <v>4.3</v>
       </c>
       <c r="H108" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I108" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J108" s="12">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A109" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D109" s="12" t="s">
         <v>68</v>
@@ -4632,30 +4634,30 @@
         <v>69</v>
       </c>
       <c r="F109" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G109" s="12">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="H109" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I109" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J109" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A110" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D110" s="12" t="s">
         <v>68</v>
@@ -4664,30 +4666,30 @@
         <v>69</v>
       </c>
       <c r="F110" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G110" s="12">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="H110" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I110" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J110" s="12">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="111" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A111" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D111" s="12" t="s">
         <v>68</v>
@@ -4696,16 +4698,16 @@
         <v>69</v>
       </c>
       <c r="F111" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G111" s="12">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="H111" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I111" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J111" s="12">
         <v>4</v>
@@ -4713,13 +4715,13 @@
     </row>
     <row r="112" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A112" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D112" s="12" t="s">
         <v>68</v>
@@ -4728,30 +4730,30 @@
         <v>69</v>
       </c>
       <c r="F112" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G112" s="12">
-        <v>4</v>
+        <v>6.1</v>
       </c>
       <c r="H112" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I112" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J112" s="12">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A113" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D113" s="12" t="s">
         <v>68</v>
@@ -4760,30 +4762,30 @@
         <v>69</v>
       </c>
       <c r="F113" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G113" s="12">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="H113" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I113" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J113" s="12">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A114" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D114" s="12" t="s">
         <v>68</v>
@@ -4792,16 +4794,16 @@
         <v>69</v>
       </c>
       <c r="F114" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G114" s="12">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="H114" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I114" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J114" s="12">
         <v>7</v>
@@ -4809,13 +4811,13 @@
     </row>
     <row r="115" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A115" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>237</v>
+        <v>171</v>
       </c>
       <c r="D115" s="12" t="s">
         <v>68</v>
@@ -4824,16 +4826,16 @@
         <v>69</v>
       </c>
       <c r="F115" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G115" s="12">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="H115" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I115" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J115" s="12">
         <v>4</v>
@@ -4841,13 +4843,13 @@
     </row>
     <row r="116" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A116" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>237</v>
+        <v>171</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D116" s="12" t="s">
         <v>68</v>
@@ -4856,16 +4858,16 @@
         <v>69</v>
       </c>
       <c r="F116" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G116" s="12">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="H116" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I116" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J116" s="12">
         <v>4</v>
@@ -4873,13 +4875,13 @@
     </row>
     <row r="117" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A117" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B117" s="12" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D117" s="12" t="s">
         <v>68</v>
@@ -4888,30 +4890,30 @@
         <v>69</v>
       </c>
       <c r="F117" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G117" s="12">
-        <v>8.5</v>
+        <v>5.4</v>
       </c>
       <c r="H117" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I117" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J117" s="12">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="118" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A118" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B118" s="12" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D118" s="12" t="s">
         <v>68</v>
@@ -4920,30 +4922,30 @@
         <v>69</v>
       </c>
       <c r="F118" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G118" s="12">
-        <v>3.3</v>
+        <v>6.4</v>
       </c>
       <c r="H118" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I118" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J118" s="12">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A119" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B119" s="12" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>180</v>
+        <v>236</v>
       </c>
       <c r="D119" s="12" t="s">
         <v>68</v>
@@ -4952,30 +4954,30 @@
         <v>69</v>
       </c>
       <c r="F119" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G119" s="12">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="H119" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I119" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J119" s="12">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A120" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B120" s="12" t="s">
-        <v>180</v>
+        <v>236</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D120" s="12" t="s">
         <v>68</v>
@@ -4984,30 +4986,30 @@
         <v>69</v>
       </c>
       <c r="F120" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G120" s="12">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="H120" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I120" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J120" s="12">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="121" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A121" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B121" s="12" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D121" s="12" t="s">
         <v>68</v>
@@ -5016,30 +5018,30 @@
         <v>69</v>
       </c>
       <c r="F121" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G121" s="12">
-        <v>3.6</v>
+        <v>8.5</v>
       </c>
       <c r="H121" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I121" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J121" s="12">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="122" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A122" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D122" s="12" t="s">
         <v>68</v>
@@ -5048,16 +5050,16 @@
         <v>69</v>
       </c>
       <c r="F122" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G122" s="12">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="H122" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I122" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J122" s="12">
         <v>4</v>
@@ -5065,13 +5067,13 @@
     </row>
     <row r="123" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A123" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B123" s="12" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D123" s="12" t="s">
         <v>68</v>
@@ -5080,30 +5082,30 @@
         <v>69</v>
       </c>
       <c r="F123" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G123" s="12">
-        <v>2.8</v>
+        <v>7</v>
       </c>
       <c r="H123" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I123" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J123" s="12">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A124" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D124" s="12" t="s">
         <v>68</v>
@@ -5112,30 +5114,30 @@
         <v>69</v>
       </c>
       <c r="F124" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G124" s="12">
-        <v>8.6</v>
+        <v>2</v>
       </c>
       <c r="H124" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I124" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J124" s="12">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A125" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D125" s="12" t="s">
         <v>68</v>
@@ -5144,16 +5146,16 @@
         <v>69</v>
       </c>
       <c r="F125" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G125" s="12">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="H125" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I125" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J125" s="12">
         <v>4</v>
@@ -5161,13 +5163,13 @@
     </row>
     <row r="126" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A126" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B126" s="12" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D126" s="12" t="s">
         <v>68</v>
@@ -5176,30 +5178,30 @@
         <v>69</v>
       </c>
       <c r="F126" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G126" s="12">
-        <v>8.1999999999999993</v>
+        <v>3.2</v>
       </c>
       <c r="H126" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I126" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J126" s="12">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A127" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B127" s="12" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D127" s="12" t="s">
         <v>68</v>
@@ -5208,30 +5210,30 @@
         <v>69</v>
       </c>
       <c r="F127" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G127" s="12">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="H127" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I127" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J127" s="12">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A128" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B128" s="12" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D128" s="12" t="s">
         <v>68</v>
@@ -5240,30 +5242,30 @@
         <v>69</v>
       </c>
       <c r="F128" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G128" s="12">
-        <v>8.6999999999999993</v>
+        <v>8.6</v>
       </c>
       <c r="H128" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I128" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J128" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="129" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A129" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B129" s="12" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D129" s="12" t="s">
         <v>68</v>
@@ -5272,7 +5274,7 @@
         <v>69</v>
       </c>
       <c r="F129" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G129" s="12">
         <v>3.3</v>
@@ -5281,7 +5283,7 @@
         <v>70</v>
       </c>
       <c r="I129" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J129" s="12">
         <v>4</v>
@@ -5289,13 +5291,13 @@
     </row>
     <row r="130" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A130" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B130" s="12" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D130" s="12" t="s">
         <v>68</v>
@@ -5304,7 +5306,7 @@
         <v>69</v>
       </c>
       <c r="F130" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G130" s="12">
         <v>8.1999999999999993</v>
@@ -5313,21 +5315,21 @@
         <v>70</v>
       </c>
       <c r="I130" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J130" s="12">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A131" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B131" s="12" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D131" s="12" t="s">
         <v>68</v>
@@ -5336,30 +5338,30 @@
         <v>69</v>
       </c>
       <c r="F131" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G131" s="12">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="H131" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I131" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J131" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A132" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B132" s="12" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D132" s="12" t="s">
         <v>68</v>
@@ -5368,30 +5370,30 @@
         <v>69</v>
       </c>
       <c r="F132" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G132" s="12">
-        <v>8.5</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="H132" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I132" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J132" s="12">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A133" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B133" s="12" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D133" s="12" t="s">
         <v>68</v>
@@ -5400,7 +5402,7 @@
         <v>69</v>
       </c>
       <c r="F133" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G133" s="12">
         <v>3.3</v>
@@ -5409,7 +5411,7 @@
         <v>70</v>
       </c>
       <c r="I133" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J133" s="12">
         <v>4</v>
@@ -5417,13 +5419,13 @@
     </row>
     <row r="134" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A134" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B134" s="12" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D134" s="12" t="s">
         <v>68</v>
@@ -5432,16 +5434,16 @@
         <v>69</v>
       </c>
       <c r="F134" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G134" s="12">
-        <v>7.8</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="H134" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I134" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J134" s="12">
         <v>8</v>
@@ -5449,13 +5451,13 @@
     </row>
     <row r="135" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A135" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B135" s="12" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D135" s="12" t="s">
         <v>68</v>
@@ -5464,16 +5466,16 @@
         <v>69</v>
       </c>
       <c r="F135" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G135" s="12">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="H135" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I135" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J135" s="12">
         <v>4</v>
@@ -5481,13 +5483,13 @@
     </row>
     <row r="136" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A136" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B136" s="12" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D136" s="12" t="s">
         <v>68</v>
@@ -5496,30 +5498,30 @@
         <v>69</v>
       </c>
       <c r="F136" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G136" s="12">
-        <v>2.9</v>
+        <v>8.5</v>
       </c>
       <c r="H136" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I136" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J136" s="12">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A137" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B137" s="12" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D137" s="12" t="s">
         <v>68</v>
@@ -5528,30 +5530,30 @@
         <v>69</v>
       </c>
       <c r="F137" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G137" s="12">
-        <v>8.3000000000000007</v>
+        <v>3.3</v>
       </c>
       <c r="H137" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I137" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J137" s="12">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A138" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B138" s="12" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D138" s="12" t="s">
         <v>68</v>
@@ -5560,30 +5562,30 @@
         <v>69</v>
       </c>
       <c r="F138" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G138" s="12">
-        <v>3.3</v>
+        <v>7.8</v>
       </c>
       <c r="H138" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I138" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J138" s="12">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="139" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A139" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B139" s="12" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D139" s="12" t="s">
         <v>68</v>
@@ -5592,30 +5594,30 @@
         <v>69</v>
       </c>
       <c r="F139" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G139" s="12">
-        <v>8.6</v>
+        <v>3.2</v>
       </c>
       <c r="H139" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I139" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J139" s="12">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A140" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B140" s="12" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D140" s="12" t="s">
         <v>68</v>
@@ -5624,30 +5626,30 @@
         <v>69</v>
       </c>
       <c r="F140" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G140" s="12">
-        <v>9</v>
+        <v>2.9</v>
       </c>
       <c r="H140" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I140" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J140" s="12">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A141" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B141" s="12" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
       <c r="D141" s="12" t="s">
         <v>68</v>
@@ -5656,16 +5658,16 @@
         <v>69</v>
       </c>
       <c r="F141" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G141" s="12">
-        <v>8.9</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="H141" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I141" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J141" s="12">
         <v>9</v>
@@ -5673,13 +5675,13 @@
     </row>
     <row r="142" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A142" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B142" s="12" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D142" s="12" t="s">
         <v>68</v>
@@ -5688,16 +5690,16 @@
         <v>69</v>
       </c>
       <c r="F142" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G142" s="12">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="H142" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I142" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J142" s="12">
         <v>4</v>
@@ -5705,13 +5707,13 @@
     </row>
     <row r="143" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A143" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B143" s="12" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D143" s="12" t="s">
         <v>68</v>
@@ -5720,30 +5722,30 @@
         <v>69</v>
       </c>
       <c r="F143" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G143" s="12">
-        <v>2.4</v>
+        <v>8.6</v>
       </c>
       <c r="H143" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I143" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J143" s="12">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="144" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A144" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B144" s="12" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D144" s="12" t="s">
         <v>68</v>
@@ -5752,30 +5754,30 @@
         <v>69</v>
       </c>
       <c r="F144" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G144" s="12">
-        <v>3.7</v>
+        <v>9</v>
       </c>
       <c r="H144" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I144" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J144" s="12">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="145" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A145" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B145" s="12" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="D145" s="12" t="s">
         <v>68</v>
@@ -5784,30 +5786,30 @@
         <v>69</v>
       </c>
       <c r="F145" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G145" s="12">
-        <v>6.4</v>
+        <v>8.9</v>
       </c>
       <c r="H145" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I145" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J145" s="12">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A146" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B146" s="12" t="s">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D146" s="12" t="s">
         <v>68</v>
@@ -5816,16 +5818,16 @@
         <v>69</v>
       </c>
       <c r="F146" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G146" s="12">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="H146" s="12" t="s">
         <v>70</v>
       </c>
       <c r="I146" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J146" s="12">
         <v>4</v>
@@ -5833,182 +5835,176 @@
     </row>
     <row r="147" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A147" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="B147" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="C147" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="D147" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E147" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F147" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="G147" s="12">
+        <v>2.4</v>
+      </c>
+      <c r="H147" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I147" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="J147" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="148" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A148" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="B148" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="C148" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="D148" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E148" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F148" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="G148" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H148" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I148" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="J148" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A149" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="B149" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="C149" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="D149" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E149" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F149" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="G149" s="12">
+        <v>6.4</v>
+      </c>
+      <c r="H149" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I149" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="J149" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="150" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A150" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="B150" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C150" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="D150" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E150" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F150" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="G150" s="12">
+        <v>3.3</v>
+      </c>
+      <c r="H150" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I150" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="J150" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A151" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="B151" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="C151" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="B147" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="C147" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="D147" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E147" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F147" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="G147" s="12">
+      <c r="D151" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E151" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F151" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="G151" s="12">
         <v>5.4</v>
       </c>
-      <c r="H147" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="I147" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="J147" s="12">
+      <c r="H151" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I151" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="J151" s="12">
         <v>6</v>
-      </c>
-    </row>
-    <row r="148" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A148" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="B148" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="C148" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="D148" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="E148" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F148" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="G148" s="12">
-        <v>3</v>
-      </c>
-      <c r="H148" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="I148" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="J148" s="12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="149" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A149" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="B149" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="C149" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="D149" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="E149" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F149" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="G149" s="12">
-        <v>7</v>
-      </c>
-      <c r="H149" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="I149" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="J149" s="12">
-        <v>8</v>
-      </c>
-      <c r="R149" s="5">
-        <v>320</v>
-      </c>
-      <c r="S149" s="5">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="150" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A150" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="B150" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="C150" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="D150" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="E150" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F150" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="G150" s="12">
-        <v>12</v>
-      </c>
-      <c r="H150" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="I150" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="J150" s="12">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="151" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A151" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="B151" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="C151" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="D151" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="E151" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F151" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="G151" s="12">
-        <v>3</v>
-      </c>
-      <c r="H151" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="I151" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="J151" s="12">
-        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A152" s="12" t="s">
-        <v>245</v>
+        <v>63</v>
       </c>
       <c r="B152" s="12" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="C152" s="12" t="s">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="D152" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E152" s="12" t="s">
         <v>69</v>
@@ -6026,21 +6022,21 @@
         <v>80</v>
       </c>
       <c r="J152" s="12">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A153" s="12" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B153" s="12" t="s">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="C153" s="12" t="s">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="D153" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E153" s="12" t="s">
         <v>69</v>
@@ -6049,7 +6045,7 @@
         <v>80</v>
       </c>
       <c r="G153" s="12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H153" s="12" t="s">
         <v>70</v>
@@ -6058,355 +6054,361 @@
         <v>80</v>
       </c>
       <c r="J153" s="12">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="R153" s="5">
+        <v>320</v>
+      </c>
+      <c r="S153" s="5">
+        <v>76</v>
       </c>
     </row>
     <row r="154" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A154" s="12" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B154" s="12" t="s">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="C154" s="12" t="s">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="D154" s="12" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="E154" s="12" t="s">
         <v>69</v>
       </c>
       <c r="F154" s="12" t="s">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="G154" s="12">
-        <v>8</v>
-      </c>
-      <c r="H154" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="H154" s="12" t="s">
+        <v>70</v>
+      </c>
       <c r="I154" s="12" t="s">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="J154" s="12">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="155" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A155" s="12" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B155" s="12" t="s">
-        <v>236</v>
+        <v>208</v>
       </c>
       <c r="C155" s="12" t="s">
-        <v>239</v>
+        <v>195</v>
       </c>
       <c r="D155" s="12" t="s">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="E155" s="12" t="s">
         <v>69</v>
       </c>
       <c r="F155" s="12" t="s">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="G155" s="12">
+        <v>3</v>
+      </c>
+      <c r="H155" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I155" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="J155" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="156" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A156" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="B156" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="C156" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="D156" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="E156" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F156" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="G156" s="12">
+        <v>3</v>
+      </c>
+      <c r="H156" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I156" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="J156" s="12">
         <v>8</v>
-      </c>
-      <c r="H155" s="12"/>
-      <c r="I155" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="J155" s="12">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="156" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A156" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="B156" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="C156" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="D156" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="E156" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F156" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="G156" s="12">
-        <v>30</v>
-      </c>
-      <c r="I156" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="J156" s="12">
-        <v>30</v>
       </c>
     </row>
     <row r="157" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A157" s="12" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B157" s="12" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C157" s="12" t="s">
-        <v>238</v>
+        <v>209</v>
       </c>
       <c r="D157" s="12" t="s">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="E157" s="12" t="s">
         <v>69</v>
       </c>
       <c r="F157" s="12" t="s">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="G157" s="12">
-        <v>30</v>
-      </c>
-      <c r="H157" s="12"/>
+        <v>8</v>
+      </c>
+      <c r="H157" s="12" t="s">
+        <v>70</v>
+      </c>
       <c r="I157" s="12" t="s">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="J157" s="12">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A158" s="12" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B158" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="C158" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="D158" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="E158" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F158" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="G158" s="12">
+        <v>8</v>
+      </c>
+      <c r="H158" s="12"/>
+      <c r="I158" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="J158" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="159" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A159" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="B159" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="C159" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="D159" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="E159" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F159" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="G159" s="12">
+        <v>8</v>
+      </c>
+      <c r="H159" s="12"/>
+      <c r="I159" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="J159" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="160" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A160" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="B160" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="C160" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="D160" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="E160" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F160" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="G160" s="12">
+        <v>30</v>
+      </c>
+      <c r="I160" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="J160" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A161" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="B161" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="C161" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="D161" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="E161" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F161" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="G161" s="12">
+        <v>30</v>
+      </c>
+      <c r="H161" s="12"/>
+      <c r="I161" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="J161" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A162" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="B162" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="C162" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="D162" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="E162" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F162" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="G162" s="12">
+        <v>1</v>
+      </c>
+      <c r="H162" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I162" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="J162" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A163" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="C158" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="D158" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="E158" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F158" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="G158" s="12">
-        <v>1</v>
-      </c>
-      <c r="H158" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="I158" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="J158" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A159" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="B159" s="17"/>
-      <c r="C159" s="17"/>
-      <c r="D159" s="17"/>
-      <c r="E159" s="17"/>
-      <c r="F159" s="17"/>
-      <c r="G159" s="17"/>
-      <c r="H159" s="17"/>
-      <c r="I159" s="17"/>
-      <c r="J159" s="17"/>
-    </row>
-    <row r="160" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A160" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="B160" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="C160" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="D160" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="E160" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="F160" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="G160" s="8">
-        <v>11</v>
-      </c>
-      <c r="H160" s="7"/>
-      <c r="I160" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="J160" s="8">
-        <v>12</v>
-      </c>
-      <c r="K160" s="6"/>
-      <c r="L160" s="6"/>
-    </row>
-    <row r="161" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A161" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="B161" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="C161" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="D161" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="E161" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="F161" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="G161" s="8">
-        <v>12</v>
-      </c>
-      <c r="H161" s="7"/>
-      <c r="I161" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="J161" s="8">
-        <v>12</v>
-      </c>
-      <c r="K161" s="6"/>
-      <c r="L161" s="6"/>
-    </row>
-    <row r="162" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A162" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="B162" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="C162" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="D162" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="E162" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="F162" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="G162" s="8">
-        <v>12</v>
-      </c>
-      <c r="H162" s="7"/>
-      <c r="I162" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="J162" s="8">
-        <v>12</v>
-      </c>
-      <c r="K162" s="6"/>
-      <c r="L162" s="6"/>
-    </row>
-    <row r="163" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A163" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="B163" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="C163" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="D163" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="E163" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="F163" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="G163" s="8">
-        <v>12</v>
-      </c>
-      <c r="H163" s="7"/>
-      <c r="I163" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="J163" s="8">
-        <v>12</v>
-      </c>
-      <c r="K163" s="6"/>
-      <c r="L163" s="6"/>
+      <c r="B163" s="17"/>
+      <c r="C163" s="17"/>
+      <c r="D163" s="17"/>
+      <c r="E163" s="17"/>
+      <c r="F163" s="17"/>
+      <c r="G163" s="17"/>
+      <c r="H163" s="17"/>
+      <c r="I163" s="17"/>
+      <c r="J163" s="17"/>
     </row>
     <row r="164" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A164" s="7" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="B164" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C164" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C164" s="7" t="s">
-        <v>224</v>
-      </c>
       <c r="D164" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E164" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="E164" s="9" t="s">
-        <v>216</v>
-      </c>
       <c r="F164" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G164" s="8">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H164" s="7"/>
-      <c r="I164" s="7" t="s">
+      <c r="I164" s="9" t="s">
         <v>3</v>
       </c>
       <c r="J164" s="8">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="K164" s="6"/>
       <c r="L164" s="6"/>
     </row>
     <row r="165" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A165" s="7" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="D165" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E165" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="E165" s="9" t="s">
-        <v>216</v>
-      </c>
       <c r="F165" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G165" s="8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H165" s="7"/>
       <c r="I165" s="9" t="s">
@@ -6420,57 +6422,57 @@
     </row>
     <row r="166" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A166" s="7" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="D166" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E166" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="E166" s="7" t="s">
-        <v>216</v>
-      </c>
       <c r="F166" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G166" s="8">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H166" s="7"/>
       <c r="I166" s="9" t="s">
         <v>3</v>
       </c>
       <c r="J166" s="8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K166" s="6"/>
       <c r="L166" s="6"/>
     </row>
     <row r="167" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A167" s="7" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="D167" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E167" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="E167" s="9" t="s">
-        <v>216</v>
-      </c>
       <c r="F167" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G167" s="8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H167" s="7"/>
       <c r="I167" s="9" t="s">
@@ -6484,134 +6486,262 @@
     </row>
     <row r="168" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A168" s="7" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C168" s="7" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D168" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E168" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="E168" s="9" t="s">
-        <v>216</v>
-      </c>
       <c r="F168" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G168" s="8">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H168" s="7"/>
-      <c r="I168" s="9" t="s">
+      <c r="I168" s="7" t="s">
         <v>3</v>
       </c>
       <c r="J168" s="8">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="K168" s="6"/>
       <c r="L168" s="6"/>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A169" s="7" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C169" s="7" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="D169" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E169" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="E169" s="9" t="s">
-        <v>216</v>
-      </c>
       <c r="F169" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="G169" s="10">
-        <v>15</v>
-      </c>
-      <c r="H169" s="10"/>
+        <v>128</v>
+      </c>
+      <c r="G169" s="8">
+        <v>11</v>
+      </c>
+      <c r="H169" s="7"/>
       <c r="I169" s="9" t="s">
         <v>3</v>
       </c>
       <c r="J169" s="8">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.4">
+        <v>12</v>
+      </c>
+      <c r="K169" s="6"/>
+      <c r="L169" s="6"/>
+    </row>
+    <row r="170" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A170" s="7" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C170" s="7" t="s">
-        <v>253</v>
+        <v>227</v>
       </c>
       <c r="D170" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E170" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="E170" s="9" t="s">
-        <v>216</v>
-      </c>
       <c r="F170" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="G170" s="10">
-        <v>26</v>
-      </c>
-      <c r="H170" s="10"/>
+        <v>128</v>
+      </c>
+      <c r="G170" s="8">
+        <v>10</v>
+      </c>
+      <c r="H170" s="7"/>
       <c r="I170" s="9" t="s">
         <v>3</v>
       </c>
       <c r="J170" s="8">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.4">
+        <v>11</v>
+      </c>
+      <c r="K170" s="6"/>
+      <c r="L170" s="6"/>
+    </row>
+    <row r="171" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A171" s="7" t="s">
-        <v>255</v>
+        <v>228</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C171" s="7" t="s">
-        <v>254</v>
+        <v>229</v>
       </c>
       <c r="D171" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E171" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="E171" s="7" t="s">
-        <v>216</v>
-      </c>
       <c r="F171" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="G171" s="10">
-        <v>18</v>
-      </c>
-      <c r="H171" s="10"/>
+        <v>128</v>
+      </c>
+      <c r="G171" s="8">
+        <v>11</v>
+      </c>
+      <c r="H171" s="7"/>
       <c r="I171" s="9" t="s">
         <v>3</v>
       </c>
       <c r="J171" s="8">
+        <v>12</v>
+      </c>
+      <c r="K171" s="6"/>
+      <c r="L171" s="6"/>
+    </row>
+    <row r="172" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A172" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="B172" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C172" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="D172" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E172" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="F172" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G172" s="8">
+        <v>30</v>
+      </c>
+      <c r="H172" s="7"/>
+      <c r="I172" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="J172" s="8">
+        <v>32</v>
+      </c>
+      <c r="K172" s="6"/>
+      <c r="L172" s="6"/>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A173" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="B173" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C173" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D173" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E173" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="F173" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G173" s="10">
+        <v>15</v>
+      </c>
+      <c r="H173" s="10"/>
+      <c r="I173" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="J173" s="8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A174" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="B174" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C174" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="D174" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E174" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="F174" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G174" s="10">
+        <v>26</v>
+      </c>
+      <c r="H174" s="10"/>
+      <c r="I174" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="J174" s="8">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A175" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="B175" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C175" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="D175" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E175" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="F175" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G175" s="10">
         <v>18</v>
       </c>
+      <c r="H175" s="10"/>
+      <c r="I175" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="J175" s="8">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="F1:F171" xr:uid="{ED1BFC1E-6170-421F-B27F-ADCB2033496C}"/>
+  <autoFilter ref="F1:F175" xr:uid="{ED1BFC1E-6170-421F-B27F-ADCB2033496C}"/>
   <mergeCells count="5">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A29:J29"/>
-    <mergeCell ref="A76:J76"/>
-    <mergeCell ref="A91:J91"/>
-    <mergeCell ref="A159:J159"/>
+    <mergeCell ref="A80:J80"/>
+    <mergeCell ref="A95:J95"/>
+    <mergeCell ref="A163:J163"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
